--- a/data/dividends_info_20261006.xlsx
+++ b/data/dividends_info_20261006.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>51.59999847412109</v>
+        <v>52</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1744186098089472</v>
+        <v>0.1730769230769231</v>
       </c>
       <c r="J2" t="n">
         <v>160</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>62.29999923706055</v>
+        <v>61.90000152587891</v>
       </c>
       <c r="I3" t="n">
-        <v>1.123595519377774</v>
+        <v>1.130856191832801</v>
       </c>
       <c r="J3" t="n">
         <v>139</v>
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>8.880000114440918</v>
+        <v>8.979999542236328</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6756756669679118</v>
+        <v>0.6681514817210997</v>
       </c>
       <c r="J4" t="n">
         <v>69</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>51.59999847412109</v>
+        <v>52</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1744186098089472</v>
+        <v>0.1730769230769231</v>
       </c>
       <c r="J6" t="n">
         <v>69</v>
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2.045000076293945</v>
+        <v>2.049999952316284</v>
       </c>
       <c r="I7" t="n">
-        <v>3.765281033120711</v>
+        <v>3.756097648343753</v>
       </c>
       <c r="J7" t="n">
         <v>48</v>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>50.65000152587891</v>
+        <v>50.70000076293945</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6529121224824317</v>
+        <v>0.6522682347605292</v>
       </c>
       <c r="J8" t="n">
         <v>48</v>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>24.34000015258789</v>
+        <v>24.13500022888184</v>
       </c>
       <c r="I9" t="n">
-        <v>1.109285120408239</v>
+        <v>1.118707260988118</v>
       </c>
       <c r="J9" t="n">
         <v>48</v>
@@ -993,10 +993,10 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>6</v>
+        <v>6.019999980926514</v>
       </c>
       <c r="I12" t="n">
-        <v>3.333333333333333</v>
+        <v>3.322259146738715</v>
       </c>
       <c r="J12" t="n">
         <v>41</v>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>6.150000095367432</v>
+        <v>6.099999904632568</v>
       </c>
       <c r="I13" t="n">
-        <v>1.138211364463692</v>
+        <v>1.147541001547219</v>
       </c>
       <c r="J13" t="n">
         <v>34</v>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>8.529999732971191</v>
+        <v>8.5</v>
       </c>
       <c r="I14" t="n">
-        <v>0.7033997875531075</v>
+        <v>0.7058823529411764</v>
       </c>
       <c r="J14" t="n">
         <v>34</v>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>10.72999954223633</v>
+        <v>10.76000022888184</v>
       </c>
       <c r="I15" t="n">
-        <v>4.287045849250126</v>
+        <v>4.27509284586514</v>
       </c>
       <c r="J15" t="n">
         <v>20</v>
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>8.600000381469727</v>
+        <v>8.449999809265137</v>
       </c>
       <c r="I16" t="n">
-        <v>0.6976743876579468</v>
+        <v>0.710059187625212</v>
       </c>
       <c r="J16" t="n">
         <v>13</v>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>7.880000114440918</v>
+        <v>7.639999866485596</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4822334955346138</v>
+        <v>0.4973822076449854</v>
       </c>
       <c r="J19" t="n">
         <v>-8</v>
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>24.32500076293945</v>
+        <v>24.13500022888184</v>
       </c>
       <c r="I20" t="n">
-        <v>1.109969132709589</v>
+        <v>1.118707260988118</v>
       </c>
       <c r="J20" t="n">
         <v>-15</v>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>1.930999994277954</v>
+        <v>1.91700005531311</v>
       </c>
       <c r="I21" t="n">
-        <v>2.951838434433224</v>
+        <v>2.973395845348058</v>
       </c>
       <c r="J21" t="n">
         <v>-15</v>
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>51.59999847412109</v>
+        <v>52</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1744186098089472</v>
+        <v>0.1730769230769231</v>
       </c>
       <c r="J22" t="n">
         <v>-15</v>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>95.94999694824219</v>
+        <v>96.05000305175781</v>
       </c>
       <c r="I23" t="n">
-        <v>1.38613865794851</v>
+        <v>1.38469542711343</v>
       </c>
       <c r="J23" t="n">
         <v>-15</v>
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>6.099999904632568</v>
+        <v>6.119999885559082</v>
       </c>
       <c r="I24" t="n">
-        <v>4.918032863773797</v>
+        <v>4.901960875977926</v>
       </c>
       <c r="J24" t="n">
         <v>-22</v>
@@ -1580,7 +1580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C154"/>
+  <dimension ref="A1:C144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1739,7 +1739,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>DESTINATION ITALIA S.p.A.</t>
+          <t>Telmes S.p.A.</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1749,14 +1749,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Energy Time S.p.A.</t>
+          <t>Tecno S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1773,7 +1773,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>FOPE S.p.A.</t>
+          <t>Predict S.p.A.</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1790,7 +1790,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>GREEN OLEO S.p.A</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1800,14 +1800,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>GREEN OLEO S.p.A</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1817,14 +1817,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Predict S.p.A.</t>
+          <t>FOPE S.p.A.</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1841,7 +1841,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Tecno S.p.A. Società Benefit</t>
+          <t>Energy Time S.p.A.</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1858,7 +1858,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Telmes S.p.A.</t>
+          <t>DESTINATION ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1868,7 +1868,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -1943,7 +1943,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BRUNELLO CUCINELLI S.p.A.</t>
+          <t>Tecno S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1960,7 +1960,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>BRUNELLO CUCINELLI S.p.A.</t>
+          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1977,7 +1977,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Casta Diva Group S.p.A.</t>
+          <t>FIDIA S.p.A</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1987,14 +1987,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>FIDIA S.p.A</t>
+          <t>BRUNELLO CUCINELLI S.p.A.</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2004,14 +2004,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
+          <t>BRUNELLO CUCINELLI S.p.A.</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2028,7 +2028,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Tecno S.p.A. Società Benefit</t>
+          <t>Casta Diva Group S.p.A.</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2038,7 +2038,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -2157,7 +2157,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -2174,7 +2174,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -2232,7 +2232,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>Renovalo S.p.A.</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2242,14 +2242,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>Unicredit S.p.A.</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2259,14 +2259,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ESPE S.p.A.</t>
+          <t>Renovalo S.p.A.</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2276,14 +2276,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Moncler S.p.A.</t>
+          <t>Racing Force S.p.A.</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2293,14 +2293,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Moncler S.p.A.</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2317,7 +2317,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Racing Force S.p.A.</t>
+          <t>Moncler S.p.A.</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2327,14 +2327,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Renovalo S.p.A.</t>
+          <t>ESPE S.p.A.</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2344,14 +2344,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Unicredit S.p.A.</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2361,14 +2361,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Renovalo S.p.A.</t>
+          <t>Moncler S.p.A.</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2378,7 +2378,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2487,7 +2487,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>RedFish LongTerm Capital S.p.A.</t>
+          <t>Impianti S.p.A.</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2504,7 +2504,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Impianti S.p.A.</t>
+          <t>Indel B S.p.A.</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2521,7 +2521,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2538,7 +2538,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Indel B S.p.A.</t>
+          <t>RedFish LongTerm Capital S.p.A.</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2555,7 +2555,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>BORGOSESIA S.p.A.</t>
+          <t>eVISO S.p.A.</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2565,14 +2565,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>CREACTIVES GROUP S.p.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2582,7 +2582,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>BORGOSESIA S.p.A.</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2623,7 +2623,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>eVISO S.p.A.</t>
+          <t>CREACTIVES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2640,7 +2640,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>eVISO S.p.A.</t>
+          <t>DIGITAL BROS S.p.A.</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2657,7 +2657,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>S.S. Lazio S.p.A.</t>
+          <t>Ferretti S.p.A.</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2667,7 +2667,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -2684,14 +2684,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Ferretti S.p.A.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2708,7 +2708,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>DIGITAL BROS S.p.A.</t>
+          <t>S.S. Lazio S.p.A.</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2725,7 +2725,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>eVISO S.p.A.</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2735,14 +2735,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>DANIELI &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2752,14 +2752,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>A.B.P. Nocivelli S.p.A.</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2769,14 +2769,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>CREACTIVES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2786,19 +2786,19 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>Italgas S.p.A.</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2810,12 +2810,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Prysmian S.p.A.</t>
+          <t>Seri Industrial S.p.A.</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2827,29 +2827,29 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>STMicroelectronics N.V.</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Davide Campari-Milano N.V.</t>
+          <t>STMicroelectronics N.V.</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2861,46 +2861,46 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Davide Campari-Milano N.V.</t>
+          <t>Prysmian S.p.A.</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>DANIELI &amp; C. S.p.A.</t>
+          <t>Italgas S.p.A.</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Farmacosmo S.p.A.</t>
+          <t>DEA CAPITAL REAL ESTATE SGR S.p.A.</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2912,41 +2912,41 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>CREACTIVES GROUP S.p.A.</t>
+          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A.B.P. Nocivelli S.p.A.</t>
+          <t>AMPLIFON S.p.A.</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Seri Industrial S.p.A.</t>
+          <t>HIGH QUALITY FOOD S.p.A.</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2963,7 +2963,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>STMicroelectronics N.V.</t>
+          <t>ELICA S.p.A.</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2980,7 +2980,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>STMicroelectronics N.V.</t>
+          <t>EDISON S.p.A.</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2990,36 +2990,36 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Prysmian S.p.A.</t>
+          <t>BIESSE S.p.A.</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Italgas S.p.A.</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3031,12 +3031,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>HIGH QUALITY FOOD S.p.A.</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3048,12 +3048,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Italgas S.p.A.</t>
+          <t>Intesa Sanpaolo S.p.A.</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3065,29 +3065,29 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>ELICA S.p.A.</t>
+          <t>OPS ECOM S.p.A.</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>EDISON S.p.A.</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3099,12 +3099,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>DEA CAPITAL REAL ESTATE SGR S.p.A.</t>
+          <t>VNE S.p.A.</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3116,12 +3116,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>AMPLIFON S.p.A.</t>
+          <t>Lottomatica Group S.p.A.</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3133,29 +3133,29 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>AMPLIFON S.p.A.</t>
+          <t>JUVENTUS F.C. S.p.A.</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
+          <t>UNIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3167,12 +3167,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>BIESSE S.p.A.</t>
+          <t>Nusco S.p.A.</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3184,80 +3184,80 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>Ferrari N.V.</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>Ferrari N.V.</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Intesa Sanpaolo S.p.A.</t>
+          <t>Lottomatica Group S.p.A.</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>OPS ECOM S.p.A.</t>
+          <t>BANCA SISTEMA S.p.A.</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>SOGES GROUP S.p.A.</t>
+          <t>Nexi S.p.A.</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3269,29 +3269,29 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>VNE S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Lottomatica Group S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3303,12 +3303,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>UNIDATA S.p.A.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3320,46 +3320,46 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Lottomatica Group S.p.A.</t>
+          <t>EDILIZIACROBATICA S.p.A.</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Nusco S.p.A.</t>
+          <t>CELLULARLINE S.p.A.</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Ferrari N.V.</t>
+          <t>CELLULARLINE S.p.A.</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -3371,41 +3371,41 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Ferrari N.V.</t>
+          <t>Bper Banca S.P.A.</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>JUVENTUS F.C. S.p.A.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>CELLULARLINE S.p.A.</t>
+          <t>TELECOM ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -3422,7 +3422,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>CELLULARLINE S.p.A.</t>
+          <t>Ariston Holding N.V.</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -3439,7 +3439,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>EDILIZIACROBATICA S.p.A.</t>
+          <t>Anima Holding S.p.A.</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -3456,7 +3456,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -3473,7 +3473,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>BANCA SISTEMA S.p.A.</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -3490,7 +3490,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>TELECOM ITALIA S.p.A.</t>
+          <t>Ariston Holding N.V.</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -3507,12 +3507,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>SIT S.p.A.</t>
+          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -3524,12 +3524,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>Nexi S.p.A.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -3541,12 +3541,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Nexi S.p.A.</t>
+          <t>Pirelli &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -3558,12 +3558,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>SIT S.p.A.</t>
+          <t>TELECOM ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -3575,46 +3575,46 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>BANCA SISTEMA S.p.A.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Ariston Holding N.V.</t>
+          <t>Banco BPM S.p.A.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Ariston Holding N.V.</t>
+          <t>Leonardo S.p.A.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -3626,12 +3626,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Anima Holding S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -3643,41 +3643,41 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Bper Banca S.P.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>BANCA SISTEMA S.p.A.</t>
+          <t>Comer Industries S.p.A.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
+          <t>Cementir Holding N.V.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -3711,7 +3711,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Pirelli &amp; C. S.p.A.</t>
+          <t>CREDITO EMILIANO S.p.A.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -3728,7 +3728,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>TELECOM ITALIA S.p.A.</t>
+          <t>Kruso Kapital S.p.A.</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -3738,14 +3738,14 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Banco BPM S.p.A.</t>
+          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -3762,7 +3762,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>CREDITO EMILIANO S.p.A.</t>
+          <t>Intred S.p.A.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -3779,7 +3779,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Cementir Holding N.V.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -3789,14 +3789,14 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Comer Industries S.p.A.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -3813,7 +3813,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>ZIGNAGO VETRO S.p.A.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -3823,14 +3823,14 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -3840,14 +3840,14 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -3857,14 +3857,14 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Leonardo S.p.A.</t>
+          <t>BUZZI S.p.A.</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -3881,7 +3881,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Nexi S.p.A.</t>
+          <t>BREMBO N.V.</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -3891,14 +3891,14 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Kruso Kapital S.p.A.</t>
+          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -3915,7 +3915,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>ZIGNAGO VETRO S.p.A.</t>
+          <t>Arterra Bioscience S.p.A.</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -3932,7 +3932,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Intred S.p.A.</t>
+          <t>AZIMUT HOLDING S.p.A.</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -3949,7 +3949,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -3959,14 +3959,14 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -3976,14 +3976,14 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
+          <t>Generalfinance S.p.A.</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -4000,7 +4000,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>BUZZI S.p.A.</t>
+          <t>Iveco Group N.V.</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -4017,7 +4017,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>BREMBO N.V.</t>
+          <t>Growens S.p.A.</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -4026,176 +4026,6 @@
         </is>
       </c>
       <c r="C144" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>2026-11-05</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>Arterra Bioscience S.p.A.</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>2026-11-05</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>AZIMUT HOLDING S.p.A.</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>2026-11-05</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>ASCOPIAVE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>2026-11-05</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>ASCOPIAVE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>2026-11-05</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>WIIT S.p.A.</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>2026-11-05</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>WIIT S.p.A.</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>2026-11-05</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>Generalfinance S.p.A.</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>2026-11-05</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>Iveco Group N.V.</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>2026-11-05</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>Growens S.p.A.</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>2026-11-05</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
         <is>
           <t>Additional Periodic Financial Information</t>
         </is>
@@ -4225,622 +4055,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C36"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>ASCOPIAVE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-11-05</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>ASCOPIAVE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-11-05</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>AZIMUT HOLDING S.p.A.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-11-05</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Arterra Bioscience S.p.A.</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-11-05</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-11-05</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>BREMBO N.V.</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-11-05</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>BUZZI S.p.A.</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-11-05</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-11-05</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Banca Profilo S.p.A.</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2026-11-05</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Banco BPM S.p.A.</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2026-11-05</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>CREDITO EMILIANO S.p.A.</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2026-11-05</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Cementir Holding N.V.</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2026-11-05</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Comer Industries S.p.A.</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2026-11-05</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2026-11-05</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2026-11-05</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>FinecoBank S.p.A.</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2026-11-05</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Generalfinance S.p.A.</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2026-11-05</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Growens S.p.A.</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2026-11-05</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>INTERCOS S.p.A.</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2026-11-05</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>INTERCOS S.p.A.</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2026-11-05</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Intred S.p.A.</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2026-11-05</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Iveco Group N.V.</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2026-11-05</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Kruso Kapital S.p.A.</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2026-11-05</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Leonardo S.p.A.</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2026-11-05</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>MARZOCCHI POMPE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2026-11-05</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Nexi S.p.A.</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2026-11-05</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Pirelli &amp; C. S.p.A.</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2026-11-05</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>STMicroelectronics N.V.</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>STMicroelectronics N.V.</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>TELECOM ITALIA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>2026-11-05</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>WIIT S.p.A.</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>2026-11-05</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>WIIT S.p.A.</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>2026-11-05</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Yakkyo S.p.A.</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>ZIGNAGO VETRO S.p.A.</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>2026-11-05</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>